--- a/client/public/upload-visits.xlsx
+++ b/client/public/upload-visits.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sahas Deneth\VMS-FINAL-HOSTED\VisitorManagementSystem-Final-\client\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{328C589D-39EB-4EA6-B380-F3384225078C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95F64F13-32B6-4363-9709-F206C26228B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="665" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -229,11 +229,11 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -241,7 +241,159 @@
   </cellStyles>
   <dxfs count="16">
     <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="165" formatCode="yyyy/mm/dd"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -260,166 +412,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="165" formatCode="yyyy/mm/dd"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -531,17 +524,17 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2786944E-3B55-4AC9-9CEA-04D86C4F5A7A}" name="Table1" displayName="Table1" ref="A2:L1048571" totalsRowShown="0" headerRowDxfId="15" headerRowBorderDxfId="14" tableBorderDxfId="13" totalsRowBorderDxfId="12">
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{FBEE452D-65C7-4BC0-A123-EC62BABBF281}" name="Factory" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{516B45B9-9F59-4B9E-9B4F-896D7A470327}" name="Department" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{6FCB732C-45A0-4B3B-A7EE-077A4D515FCF}" name="Visitor's Name" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{41D50F7A-2B80-4E87-B0FC-F32B6E297320}" name="NIC Number" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{2635602C-10FE-4A5B-8BB4-74EE3726DF30}" name="Mobile No" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{05356C70-8394-40A2-9629-2898D5B22722}" name="Email" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{61D8A246-F6AF-4DB9-B4EF-89284D884E28}" name="Visiting Date From" dataDxfId="5"/>
-    <tableColumn id="13" xr3:uid="{C81687E6-AA8B-406D-B827-AFB63CC1E4B4}" name="Visiting Date To" dataDxfId="0"/>
-    <tableColumn id="8" xr3:uid="{756BBDC7-A75A-4B06-9E1A-0C5FA23DFCEF}" name="In-Time" dataDxfId="1"/>
-    <tableColumn id="9" xr3:uid="{CE808464-E964-42A4-8120-5B2084FBFFF3}" name="Out-Time" dataDxfId="4"/>
-    <tableColumn id="10" xr3:uid="{9A3E8A8C-2EE0-481F-864D-D47D1FC7C6C5}" name="Vehicle Type" dataDxfId="3"/>
-    <tableColumn id="11" xr3:uid="{7347A1B7-5C85-4C0D-8999-9AFA50D84AFC}" name="Vehicle No" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{516B45B9-9F59-4B9E-9B4F-896D7A470327}" name="Department" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{6FCB732C-45A0-4B3B-A7EE-077A4D515FCF}" name="Visitor's Name" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{41D50F7A-2B80-4E87-B0FC-F32B6E297320}" name="NIC Number" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{2635602C-10FE-4A5B-8BB4-74EE3726DF30}" name="Mobile No" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{05356C70-8394-40A2-9629-2898D5B22722}" name="Email" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{61D8A246-F6AF-4DB9-B4EF-89284D884E28}" name="Visiting Date From" dataDxfId="4"/>
+    <tableColumn id="13" xr3:uid="{C81687E6-AA8B-406D-B827-AFB63CC1E4B4}" name="Visiting Date To" dataDxfId="10"/>
+    <tableColumn id="8" xr3:uid="{756BBDC7-A75A-4B06-9E1A-0C5FA23DFCEF}" name="In-Time" dataDxfId="9"/>
+    <tableColumn id="9" xr3:uid="{CE808464-E964-42A4-8120-5B2084FBFFF3}" name="Out-Time" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{9A3E8A8C-2EE0-481F-864D-D47D1FC7C6C5}" name="Vehicle Type" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{7347A1B7-5C85-4C0D-8999-9AFA50D84AFC}" name="Vehicle No" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -815,41 +808,41 @@
   <cols>
     <col min="1" max="1" width="24.77734375" style="3" customWidth="1"/>
     <col min="2" max="2" width="16.77734375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.21875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.21875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.21875" style="7" customWidth="1"/>
+    <col min="4" max="4" width="17.21875" style="7" customWidth="1"/>
     <col min="5" max="5" width="18.44140625" style="7" customWidth="1"/>
-    <col min="6" max="6" width="32.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="32.6640625" style="7" customWidth="1"/>
     <col min="7" max="7" width="18" style="6" customWidth="1"/>
     <col min="8" max="8" width="20.109375" style="6" customWidth="1"/>
     <col min="9" max="9" width="21.44140625" style="2" customWidth="1"/>
     <col min="10" max="10" width="16" style="2" customWidth="1"/>
-    <col min="11" max="11" width="13.6640625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="20.5546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.6640625" style="7" customWidth="1"/>
+    <col min="12" max="12" width="20.5546875" style="7" customWidth="1"/>
     <col min="13" max="13" width="17.77734375" customWidth="1"/>
     <col min="14" max="14" width="13.77734375" customWidth="1"/>
     <col min="15" max="15" width="10.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="67.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
     </row>
     <row r="2" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">

--- a/client/public/upload-visits.xlsx
+++ b/client/public/upload-visits.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sahas Deneth\VMS-FINAL-HOSTED\VisitorManagementSystem-Final-\client\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95F64F13-32B6-4363-9709-F206C26228B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEBB8183-8132-4F82-8764-4CB25ECA1D24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="665" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,30 +38,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
-    <t>Factory</t>
-  </si>
-  <si>
-    <t>Department</t>
-  </si>
-  <si>
-    <t>Visitor's Name</t>
-  </si>
-  <si>
-    <t>NIC Number</t>
-  </si>
-  <si>
-    <t>Mobile No</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>In-Time</t>
-  </si>
-  <si>
-    <t>Out-Time</t>
-  </si>
-  <si>
     <t>Vehicle Type</t>
   </si>
   <si>
@@ -69,7 +45,176 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Instructions: Please follow these when using the Excel data import function:
+      <t xml:space="preserve">Factory </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Department </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Visitor's Name </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">NIC Number </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mobile No </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Email </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Visiting Date From </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Visiting Date To </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">In-Time </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Out-Time </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Instructions: Please follow these when using the Excel data import function:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
    </t>
     </r>
     <r>
@@ -80,16 +225,31 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> - Complete all cells in each row. Do not leave any cells blank.
+      <t xml:space="preserve"> - Please complete all cells in each row; </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>only the vehicle details can be left empty.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
     - Do not insert empty rows between data entries. Data must start from Row 3.
     - Do not modify the template structure manually.</t>
     </r>
-  </si>
-  <si>
-    <t>Visiting Date From</t>
-  </si>
-  <si>
-    <t>Visiting Date To</t>
   </si>
 </sst>
 </file>
@@ -100,7 +260,7 @@
     <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
     <numFmt numFmtId="165" formatCode="yyyy/mm/dd"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -137,8 +297,31 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -151,8 +334,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -212,11 +401,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -232,7 +458,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -292,6 +524,61 @@
       </border>
     </dxf>
     <dxf>
+      <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="yyyy/mm/dd"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="yyyy/mm/dd"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -309,23 +596,6 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="yyyy/mm/dd"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -390,44 +660,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="yyyy/mm/dd"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -523,16 +755,16 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2786944E-3B55-4AC9-9CEA-04D86C4F5A7A}" name="Table1" displayName="Table1" ref="A2:L1048571" totalsRowShown="0" headerRowDxfId="15" headerRowBorderDxfId="14" tableBorderDxfId="13" totalsRowBorderDxfId="12">
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{FBEE452D-65C7-4BC0-A123-EC62BABBF281}" name="Factory" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{516B45B9-9F59-4B9E-9B4F-896D7A470327}" name="Department" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{6FCB732C-45A0-4B3B-A7EE-077A4D515FCF}" name="Visitor's Name" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{41D50F7A-2B80-4E87-B0FC-F32B6E297320}" name="NIC Number" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{2635602C-10FE-4A5B-8BB4-74EE3726DF30}" name="Mobile No" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{05356C70-8394-40A2-9629-2898D5B22722}" name="Email" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{61D8A246-F6AF-4DB9-B4EF-89284D884E28}" name="Visiting Date From" dataDxfId="4"/>
-    <tableColumn id="13" xr3:uid="{C81687E6-AA8B-406D-B827-AFB63CC1E4B4}" name="Visiting Date To" dataDxfId="10"/>
-    <tableColumn id="8" xr3:uid="{756BBDC7-A75A-4B06-9E1A-0C5FA23DFCEF}" name="In-Time" dataDxfId="9"/>
-    <tableColumn id="9" xr3:uid="{CE808464-E964-42A4-8120-5B2084FBFFF3}" name="Out-Time" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{FBEE452D-65C7-4BC0-A123-EC62BABBF281}" name="Factory *" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{516B45B9-9F59-4B9E-9B4F-896D7A470327}" name="Department *" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{6FCB732C-45A0-4B3B-A7EE-077A4D515FCF}" name="Visitor's Name *" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{41D50F7A-2B80-4E87-B0FC-F32B6E297320}" name="NIC Number *" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{2635602C-10FE-4A5B-8BB4-74EE3726DF30}" name="Mobile No *" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{05356C70-8394-40A2-9629-2898D5B22722}" name="Email *" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{61D8A246-F6AF-4DB9-B4EF-89284D884E28}" name="Visiting Date From *" dataDxfId="5"/>
+    <tableColumn id="13" xr3:uid="{C81687E6-AA8B-406D-B827-AFB63CC1E4B4}" name="Visiting Date To *" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{756BBDC7-A75A-4B06-9E1A-0C5FA23DFCEF}" name="In-Time *" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{CE808464-E964-42A4-8120-5B2084FBFFF3}" name="Out-Time *" dataDxfId="2"/>
     <tableColumn id="10" xr3:uid="{9A3E8A8C-2EE0-481F-864D-D47D1FC7C6C5}" name="Vehicle Type" dataDxfId="1"/>
     <tableColumn id="11" xr3:uid="{7347A1B7-5C85-4C0D-8999-9AFA50D84AFC}" name="Vehicle No" dataDxfId="0"/>
   </tableColumns>
@@ -823,21 +1055,21 @@
     <col min="15" max="15" width="10.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="67.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="82.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
+        <v>12</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="11"/>
       <c r="M1" s="8"/>
       <c r="N1" s="8"/>
       <c r="O1" s="8"/>
@@ -846,40 +1078,40 @@
     </row>
     <row r="2" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="L2" s="5" t="s">
         <v>1</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="1048572" customFormat="1" x14ac:dyDescent="0.3"/>
